--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1603.08</v>
+        <v>1589.51</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>27412.71</v>
+        <v>27125.63</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24521.9</v>
+        <v>24691.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43764.14</v>
+        <v>43990.16</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2137.44</v>
+        <v>2152.53</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>628.23</v>
+        <v>625.98</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>36292.67</v>
+        <v>36214.13</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>54138.84</v>
+        <v>53680.23</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2694.33</v>
+        <v>2723.23</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4536.31</v>
+        <v>4561.12</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2262.53</v>
+        <v>2218.4</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>45137.5</v>
+        <v>45824.67</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10940.7</v>
+        <v>11107.26</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>26570.26</v>
+        <v>26974.77</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30479.74</v>
+        <v>30448.31</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1071.9</v>
+        <v>1065.39</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8153.39</v>
+        <v>8121.92</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2320.13</v>
+        <v>2332.14</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1648.54</v>
+        <v>1655.04</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26494.54</v>
+        <v>26376.07</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1362.8</v>
+        <v>1368.43</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1257.29</v>
+        <v>1262.48</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3889.75</v>
+        <v>3831.74</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1648.55</v>
+        <v>1623.96</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10599.93</v>
+        <v>10441.82</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1328.07</v>
+        <v>1322.35</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5283.22</v>
+        <v>5169.55</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1293.71</v>
+        <v>1252.45</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>102694.53</v>
+        <v>100669.25</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3114.51</v>
+        <v>3058.03</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2646.22</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2646.22</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>37681.06</v>
+        <v>38144.81</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2227.45</v>
+        <v>2257.11</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>556.51</v>
+        <v>563.77</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1242.92</v>
+        <v>1246.83</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1588.17</v>
+        <v>1574.62</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1455.82</v>
+        <v>1443.4</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1671.05</v>
+        <v>1663.73</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>620.6900000000001</v>
+        <v>619.29</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>38910.68</v>
+        <v>39101.82</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>788.24</v>
+        <v>782.26</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1217.64</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>227.15</v>
+        <v>224.02</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12751.16</v>
+        <v>12672.11</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>38645.26</v>
+        <v>37888.82</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>952946-220-CM25</t>
+          <t>5751-20-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1589.51</v>
+        <v>912.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079694-413-CM25</t>
+          <t>952946-209-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>27125.63</v>
+        <v>47733.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>299-257-CM25</t>
+          <t>952946-220-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24691.78</v>
+        <v>1589.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>952946-230-CM25</t>
+          <t>1079694-413-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43990.16</v>
+        <v>27125.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>952946-236-CM25</t>
+          <t>299-257-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2152.53</v>
+        <v>24691.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>766116-2-CM25</t>
+          <t>952946-230-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>625.98</v>
+        <v>43990.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079694-512-CM25</t>
+          <t>952946-236-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>36214.13</v>
+        <v>2152.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>912853-27-SE25</t>
+          <t>766116-2-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,24 +989,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>53680.23</v>
+        <v>625.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1426100-220-CM25</t>
+          <t>1079694-512-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2723.23</v>
+        <v>36214.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>707424-159-CM25</t>
+          <t>912853-27-SE25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1115,20 +1111,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4561.12</v>
+        <v>53680.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>952946-1-CM26</t>
+          <t>1426100-220-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2218.4</v>
+        <v>2723.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079694-17-CM26</t>
+          <t>707424-159-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>45824.67</v>
+        <v>4561.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4777-40-CM26</t>
+          <t>952946-1-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11107.26</v>
+        <v>2218.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4777-41-CM26</t>
+          <t>4777-40-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>26974.77</v>
+        <v>11107.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1079694-46-CM26</t>
+          <t>4777-41-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,27 +1382,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30448.31</v>
+        <v>26974.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5751-39-CM26</t>
+          <t>1079694-17-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1065.39</v>
+        <v>45824.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4777-170-CM26</t>
+          <t>1079694-46-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,22 +1509,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8121.92</v>
+        <v>30448.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>952946-21-CM26</t>
+          <t>5751-39-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2332.14</v>
+        <v>1065.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>952946-22-CM26</t>
+          <t>4777-170-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1655.04</v>
+        <v>8121.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079694-76-CM26</t>
+          <t>952946-21-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26376.07</v>
+        <v>2332.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>926853-3-CM26</t>
+          <t>952946-22-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1368.43</v>
+        <v>1655.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1192360-14-CM26</t>
+          <t>1079694-76-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1262.48</v>
+        <v>26376.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079694-83-CM26</t>
+          <t>926853-3-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3831.74</v>
+        <v>1368.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>952946-46-CM26</t>
+          <t>1192360-14-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1623.96</v>
+        <v>1262.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4777-243-CM26</t>
+          <t>952946-46-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10441.82</v>
+        <v>1623.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1079694-88-CM26</t>
+          <t>4777-243-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1322.35</v>
+        <v>10441.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>509876-20-CM26</t>
+          <t>1079694-83-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5169.55</v>
+        <v>3831.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5418-63-CM26</t>
+          <t>1079694-88-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1252.45</v>
+        <v>1322.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>707424-15-CM26</t>
+          <t>509876-20-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,27 +2236,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,24 +2274,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>100669.25</v>
+        <v>5169.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>707424-20-CM26</t>
+          <t>5418-63-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2306,7 +2302,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2316,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2346,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3058.03</v>
+        <v>1252.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1395865-67-CM26</t>
+          <t>707424-15-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2367,7 +2363,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2377,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2400,20 +2396,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2668.67</v>
+        <v>100669.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1395865-68-CM26</t>
+          <t>707424-20-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2428,22 +2428,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2668.67</v>
+        <v>3058.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079694-104-CM26</t>
+          <t>1395865-67-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38144.81</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>952946-63-CM26</t>
+          <t>1395865-68-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2257.11</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>926853-10-CM26</t>
+          <t>1079694-104-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>563.77</v>
+        <v>38144.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>952946-76-CM26</t>
+          <t>952946-63-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1246.83</v>
+        <v>2257.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5418-93-CM26</t>
+          <t>926853-10-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1574.62</v>
+        <v>563.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5418-94-CM26</t>
+          <t>952946-76-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1443.4</v>
+        <v>1246.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>952946-87-CM26</t>
+          <t>5418-93-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1663.73</v>
+        <v>1574.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1267885-471-CM26</t>
+          <t>5418-94-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>619.29</v>
+        <v>1443.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1079694-154-CM26</t>
+          <t>952946-87-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>39101.82</v>
+        <v>1663.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5418-118-CM26</t>
+          <t>1267885-471-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>782.26</v>
+        <v>619.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5456-37-CM26</t>
+          <t>1079694-154-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1197.07</v>
+        <v>39101.82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1079694-184-CM26</t>
+          <t>5418-118-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>224.02</v>
+        <v>782.26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1723-329-CM26</t>
+          <t>5456-37-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3221,22 +3221,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3261,18 +3261,18 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12672.11</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1079694-202-CM26</t>
+          <t>1079694-184-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3322,6 +3322,128 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
+        <v>224.02</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1723-329-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>12672.11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1079694-202-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>37888.82</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5751-20-CM25</t>
+          <t>952946-2-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>912.72</v>
+        <v>990.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>952946-209-CM25</t>
+          <t>952946-6-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>47733.45</v>
+        <v>995.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>952946-220-CM25</t>
+          <t>952946-7-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1589.51</v>
+        <v>1393.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1079694-413-CM25</t>
+          <t>5592-5-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>27125.63</v>
+        <v>3199.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>299-257-CM25</t>
+          <t>5751-20-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24691.78</v>
+        <v>912.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>952946-230-CM25</t>
+          <t>707424-2-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43990.16</v>
+        <v>30927.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>952946-236-CM25</t>
+          <t>1079694-8-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2152.53</v>
+        <v>29803.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>766116-2-CM25</t>
+          <t>4062-134-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>625.98</v>
+        <v>731.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079694-512-CM25</t>
+          <t>952946-24-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>36214.13</v>
+        <v>1045.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>912853-27-SE25</t>
+          <t>1079694-22-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1111,24 +1111,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>53680.23</v>
+        <v>20625.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1426100-220-CM25</t>
+          <t>952946-41-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2723.23</v>
+        <v>1073.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>707424-159-CM25</t>
+          <t>952946-46-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4561.12</v>
+        <v>1072.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>952946-1-CM26</t>
+          <t>1079694-41-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2218.4</v>
+        <v>28529.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4777-40-CM26</t>
+          <t>509876-16-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11107.26</v>
+        <v>5171.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4777-41-CM26</t>
+          <t>707424-15-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26974.77</v>
+        <v>3811.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079694-17-CM26</t>
+          <t>4777-1905-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1488,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>45824.67</v>
+        <v>726.1799999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079694-46-CM26</t>
+          <t>1192360-20-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30448.31</v>
+        <v>1116.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5751-39-CM26</t>
+          <t>4777-1927-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1065.39</v>
+        <v>10880.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4777-170-CM26</t>
+          <t>1079694-62-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8121.92</v>
+        <v>1156.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>952946-21-CM26</t>
+          <t>4777-1930-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2332.14</v>
+        <v>13019.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>952946-22-CM26</t>
+          <t>5657-77-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1655.04</v>
+        <v>6657.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1079694-76-CM26</t>
+          <t>1079694-63-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26376.07</v>
+        <v>25387.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>926853-3-CM26</t>
+          <t>5456-25-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1368.43</v>
+        <v>1162.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1192360-14-CM26</t>
+          <t>5418-59-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1262.48</v>
+        <v>1515.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>952946-46-CM26</t>
+          <t>5418-79-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1623.96</v>
+        <v>3035.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4777-243-CM26</t>
+          <t>299-61-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10441.82</v>
+        <v>878.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1079694-83-CM26</t>
+          <t>707424-25-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3831.74</v>
+        <v>2805.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079694-88-CM26</t>
+          <t>5472-52-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1322.35</v>
+        <v>2111.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>509876-20-CM26</t>
+          <t>952946-90-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5169.55</v>
+        <v>1249.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5418-63-CM26</t>
+          <t>1079694-96-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1252.45</v>
+        <v>24230.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>707424-15-CM26</t>
+          <t>952946-99-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2396,24 +2392,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>100669.25</v>
+        <v>3724.71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>707424-20-CM26</t>
+          <t>5742-60-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2423,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2438,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.040-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2468,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3058.03</v>
+        <v>1269.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1395865-67-CM26</t>
+          <t>5742-61-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2484,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>61.979.040-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2529,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2668.67</v>
+        <v>634.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1395865-68-CM26</t>
+          <t>299-68-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2545,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2590,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2668.67</v>
+        <v>1723.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1079694-104-CM26</t>
+          <t>4062-408-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2606,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2621,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2651,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>38144.81</v>
+        <v>747.3099999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>952946-63-CM26</t>
+          <t>707424-37-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2667,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2712,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2257.11</v>
+        <v>34544.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>926853-10-CM26</t>
+          <t>299-74-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2728,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2773,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>563.77</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>952946-76-CM26</t>
+          <t>952946-118-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2789,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2809,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2834,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1246.83</v>
+        <v>1596.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5418-93-CM26</t>
+          <t>952946-120-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2850,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2865,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2895,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1574.62</v>
+        <v>72222.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5418-94-CM26</t>
+          <t>707424-40-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2911,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2926,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2956,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1443.4</v>
+        <v>568.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>952946-87-CM26</t>
+          <t>1723-411-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2972,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3017,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1663.73</v>
+        <v>14568.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1267885-471-CM26</t>
+          <t>1079694-166-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3033,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3048,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3078,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>619.29</v>
+        <v>20275.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1079694-154-CM26</t>
+          <t>952946-128-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3094,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3109,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3139,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>39101.82</v>
+        <v>2134.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5418-118-CM26</t>
+          <t>3762-3050-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3155,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3200,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>782.26</v>
+        <v>1052.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5456-37-CM26</t>
+          <t>5592-3294-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3216,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3231,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3261,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1197.07</v>
+        <v>2725.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1079694-184-CM26</t>
+          <t>952946-161-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3277,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3292,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3322,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>224.02</v>
+        <v>1053.82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1723-329-CM26</t>
+          <t>3762-3087-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3338,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3353,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3383,28 +3375,28 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>12672.11</v>
+        <v>25681.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1079694-202-CM26</t>
+          <t>1079694-241-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3419,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3444,7 +3436,4102 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
+        <v>33850.65</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5617-30-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>11719.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4777-2192-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>226.78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3789-472-CM25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.200.900-2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>17083.83</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3762-3113-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.200.900-2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>2406.34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1395865-72-CM25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>65.189.089-6</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>1829.83</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1079694-273-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>20672.29</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>952946-189-CM25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>2064.77</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>952946-192-CM25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>2072.52</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>926853-85-CM25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>521.09</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4777-2354-CM25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>175.79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1079694-331-CM25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>28912.65</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>952946-204-CM25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>357.03</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1079694-351-CM25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>24698.16</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>707424-100-CM25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>3128.69</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>952946-206-CM25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>2091.77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4777-2444-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>2859.91</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>952946-209-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>47733.45</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>707424-103-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>26771.84</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>952946-220-CM25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>1589.51</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1079694-413-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>27125.63</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>299-257-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>24691.78</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>952946-230-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>43990.16</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>952946-236-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>2152.53</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>766116-2-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>625.98</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1079694-512-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>36214.13</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>912853-27-SE25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.980.570-4</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>53680.23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1426100-220-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>2723.23</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>707424-159-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>4561.12</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>952946-1-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>2218.4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1079694-17-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>45824.67</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4777-40-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>11107.26</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4777-41-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>26974.77</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1079694-46-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>30448.31</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5751-39-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.818.002-6</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>1065.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4777-170-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>8121.92</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>952946-21-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>2332.14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>952946-22-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>1655.04</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1079694-76-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>26376.07</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>926853-3-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Valdivia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>1368.43</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1192360-14-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.978.950-4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1262.48</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>952946-46-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>1623.96</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4777-243-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>10441.82</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1079694-83-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>3831.74</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1079694-88-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>1322.35</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>509876-20-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>5169.55</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5418-63-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1252.45</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>707424-15-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>100669.25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>707424-20-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>3058.03</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1395865-68-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>65.189.089-6</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>2668.67</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1395865-67-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>65.189.089-6</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>2668.67</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1079694-104-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>38144.81</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>952946-63-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>2257.11</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>926853-10-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Valdivia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>563.77</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>952946-76-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>1246.83</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>5418-93-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>1574.62</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>5418-94-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>1443.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>952946-87-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>1663.73</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1267885-471-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>71.016.300-6</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>619.29</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1079694-154-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>39101.82</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>5418-118-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>782.26</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>5456-37-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>65.852.930-7</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>1197.07</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1079694-184-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>224.02</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1723-329-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>12672.11</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1079694-202-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
         <v>37888.82</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1079694-255-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>40987.94</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4777-668-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>749.0599999999999</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1079694-291-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>38736.49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5751-20-CM25</t>
+          <t>707424-2-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>912.72</v>
+        <v>30927.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>707424-2-CM25</t>
+          <t>1079694-8-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30927.31</v>
+        <v>29803.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079694-8-CM25</t>
+          <t>4062-134-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>29803.4</v>
+        <v>731.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4062-134-CM25</t>
+          <t>952946-24-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>731.74</v>
+        <v>1045.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>952946-24-CM25</t>
+          <t>1079694-22-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1045.34</v>
+        <v>20625.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079694-22-CM25</t>
+          <t>952946-41-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20625.15</v>
+        <v>1073.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>952946-41-CM25</t>
+          <t>952946-46-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1073.96</v>
+        <v>1072.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>952946-46-CM25</t>
+          <t>1079694-41-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1072.64</v>
+        <v>28529.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1079694-41-CM25</t>
+          <t>509876-16-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28529.75</v>
+        <v>5171.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>509876-16-CM25</t>
+          <t>707424-15-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5171.93</v>
+        <v>3811.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>707424-15-CM25</t>
+          <t>4777-1905-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3811.16</v>
+        <v>726.1799999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4777-1905-CM25</t>
+          <t>1192360-20-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>726.1799999999999</v>
+        <v>1116.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1192360-20-CM25</t>
+          <t>1079694-62-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1116.16</v>
+        <v>1156.53</v>
       </c>
     </row>
     <row r="19">
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079694-62-CM25</t>
+          <t>5657-77-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1156.53</v>
+        <v>6657.65</v>
       </c>
     </row>
     <row r="21">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5657-77-CM25</t>
+          <t>1079694-63-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6657.65</v>
+        <v>25387.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1079694-63-CM25</t>
+          <t>5456-25-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>25387.04</v>
+        <v>1162.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5456-25-CM25</t>
+          <t>5418-59-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1162.06</v>
+        <v>1515.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5418-59-CM25</t>
+          <t>5418-79-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1515.03</v>
+        <v>3035.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5418-79-CM25</t>
+          <t>707424-25-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3035.96</v>
+        <v>2805.62</v>
       </c>
     </row>
     <row r="27">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>707424-25-CM25</t>
+          <t>5472-52-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2805.62</v>
+        <v>2111.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5472-52-CM25</t>
+          <t>952946-90-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2111.91</v>
+        <v>1249.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>952946-90-CM25</t>
+          <t>1079694-96-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1249.51</v>
+        <v>24230.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1079694-96-CM25</t>
+          <t>952946-99-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>24230.83</v>
+        <v>3724.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>952946-99-CM25</t>
+          <t>5742-60-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.979.040-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3724.71</v>
+        <v>1269.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5742-60-CM25</t>
+          <t>5742-61-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1269.25</v>
+        <v>634.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5742-61-CM25</t>
+          <t>299-68-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.979.040-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>634.62</v>
+        <v>1723.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>299-68-CM25</t>
+          <t>4062-408-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1723.74</v>
+        <v>747.3099999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4062-408-CM25</t>
+          <t>707424-37-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>747.3099999999999</v>
+        <v>34544.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>707424-37-CM25</t>
+          <t>299-74-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>34544.7</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>299-74-CM25</t>
+          <t>952946-118-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>608.37</v>
+        <v>1596.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>952946-118-CM25</t>
+          <t>952946-120-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1596.34</v>
+        <v>72222.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>952946-120-CM25</t>
+          <t>707424-40-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>72222.87</v>
+        <v>568.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>707424-40-CM25</t>
+          <t>1723-411-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>568.75</v>
+        <v>14568.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1723-411-CM25</t>
+          <t>952946-128-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>14568.2</v>
+        <v>2134.27</v>
       </c>
     </row>
     <row r="43">
@@ -3076,7 +3076,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>952946-128-CM25</t>
+          <t>3762-3050-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2134.27</v>
+        <v>1052.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3762-3050-CM25</t>
+          <t>5592-3294-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1052.16</v>
+        <v>2725.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5592-3294-CM25</t>
+          <t>952946-161-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2725.12</v>
+        <v>1053.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>952946-161-CM25</t>
+          <t>3762-3087-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1053.82</v>
+        <v>25681.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3762-3087-CM25</t>
+          <t>1079694-241-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>25681.75</v>
+        <v>33850.65</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1079694-241-CM25</t>
+          <t>5617-30-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>33850.65</v>
+        <v>11719.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5617-30-CM25</t>
+          <t>4777-2192-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>11719.4</v>
+        <v>226.78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4777-2192-CM25</t>
+          <t>3789-472-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>226.78</v>
+        <v>17083.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3789-472-CM25</t>
+          <t>3762-3113-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>17083.83</v>
+        <v>2406.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3762-3113-CM25</t>
+          <t>1395865-72-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2406.34</v>
+        <v>1829.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1395865-72-CM25</t>
+          <t>1079694-273-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1829.83</v>
+        <v>20672.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1079694-273-CM25</t>
+          <t>952946-189-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>20672.29</v>
+        <v>2064.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>952946-189-CM25</t>
+          <t>952946-192-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2064.77</v>
+        <v>2072.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>952946-192-CM25</t>
+          <t>926853-85-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2072.52</v>
+        <v>521.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>926853-85-CM25</t>
+          <t>4777-2354-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>521.09</v>
+        <v>175.79</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4777-2354-CM25</t>
+          <t>1079694-331-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>175.79</v>
+        <v>28912.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079694-331-CM25</t>
+          <t>952946-204-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>28912.65</v>
+        <v>357.03</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>952946-204-CM25</t>
+          <t>1079694-351-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>357.03</v>
+        <v>24698.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1079694-351-CM25</t>
+          <t>707424-100-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>24698.16</v>
+        <v>3128.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>707424-100-CM25</t>
+          <t>952946-206-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3128.69</v>
+        <v>2091.77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>952946-206-CM25</t>
+          <t>4777-2444-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2091.77</v>
+        <v>2859.91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4777-2444-CM25</t>
+          <t>952946-209-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2859.91</v>
+        <v>47733.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>952946-209-CM25</t>
+          <t>707424-103-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>47733.45</v>
+        <v>26771.84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>707424-103-CM25</t>
+          <t>952946-220-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>26771.84</v>
+        <v>1589.51</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>952946-220-CM25</t>
+          <t>1079694-413-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1589.51</v>
+        <v>27125.63</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1079694-413-CM25</t>
+          <t>299-257-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>27125.63</v>
+        <v>24691.78</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>299-257-CM25</t>
+          <t>952946-230-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>24691.78</v>
+        <v>43990.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>952946-230-CM25</t>
+          <t>952946-236-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>43990.16</v>
+        <v>2152.53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>952946-236-CM25</t>
+          <t>766116-2-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2152.53</v>
+        <v>625.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>766116-2-CM25</t>
+          <t>1079694-512-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>625.98</v>
+        <v>36214.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1079694-512-CM25</t>
+          <t>912853-27-SE25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4954,20 +4954,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>36214.13</v>
+        <v>53680.23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>912853-27-SE25</t>
+          <t>1426100-220-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4986,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5015,24 +5019,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>53680.23</v>
+        <v>2723.23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1426100-220-CM25</t>
+          <t>707424-159-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2723.23</v>
+        <v>4561.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>707424-159-CM25</t>
+          <t>952946-1-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4561.12</v>
+        <v>2218.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>952946-1-CM26</t>
+          <t>4777-40-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2218.4</v>
+        <v>11107.26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1079694-17-CM26</t>
+          <t>4777-41-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>45824.67</v>
+        <v>26974.77</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4777-40-CM26</t>
+          <t>1079694-17-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>11107.26</v>
+        <v>45824.67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4777-41-CM26</t>
+          <t>1079694-46-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,27 +5347,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26974.77</v>
+        <v>30448.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1079694-46-CM26</t>
+          <t>5751-39-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>30448.31</v>
+        <v>1065.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5751-39-CM26</t>
+          <t>4777-170-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,22 +5474,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1065.39</v>
+        <v>8121.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4777-170-CM26</t>
+          <t>952946-21-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8121.92</v>
+        <v>2332.14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>952946-21-CM26</t>
+          <t>952946-22-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2332.14</v>
+        <v>1655.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>952946-22-CM26</t>
+          <t>1079694-76-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1655.04</v>
+        <v>26376.07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1079694-76-CM26</t>
+          <t>1192360-14-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>26376.07</v>
+        <v>1262.48</v>
       </c>
     </row>
     <row r="88">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5825,7 +5825,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1192360-14-CM26</t>
+          <t>952946-46-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1262.48</v>
+        <v>1623.96</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>952946-46-CM26</t>
+          <t>4777-243-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1623.96</v>
+        <v>10441.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4777-243-CM26</t>
+          <t>1079694-83-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5967,17 +5967,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10441.82</v>
+        <v>3831.74</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1079694-83-CM26</t>
+          <t>1079694-88-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3831.74</v>
+        <v>1322.35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1079694-88-CM26</t>
+          <t>509876-20-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1322.35</v>
+        <v>5169.55</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>509876-20-CM26</t>
+          <t>5418-63-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5169.55</v>
+        <v>1252.45</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5418-63-CM26</t>
+          <t>707424-15-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6206,22 +6206,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6239,20 +6239,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1252.45</v>
+        <v>100669.25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>707424-15-CM26</t>
+          <t>707424-20-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6267,12 +6271,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6300,24 +6304,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>100669.25</v>
+        <v>3058.03</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>707424-20-CM26</t>
+          <t>1395865-67-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6332,22 +6332,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3058.03</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="98">
@@ -6439,7 +6439,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1395865-67-CM26</t>
+          <t>1079694-104-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6454,22 +6454,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6494,13 +6494,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2668.67</v>
+        <v>38144.81</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1079694-104-CM26</t>
+          <t>952946-63-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>38144.81</v>
+        <v>2257.11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>952946-63-CM26</t>
+          <t>926853-10-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2257.11</v>
+        <v>563.77</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>926853-10-CM26</t>
+          <t>952946-76-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6677,13 +6677,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>563.77</v>
+        <v>1246.83</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>952946-76-CM26</t>
+          <t>5418-93-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6738,13 +6738,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1246.83</v>
+        <v>1574.62</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5418-93-CM26</t>
+          <t>5418-94-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6799,13 +6799,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1574.62</v>
+        <v>1443.4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5418-94-CM26</t>
+          <t>952946-87-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6860,13 +6860,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1443.4</v>
+        <v>1663.73</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>952946-87-CM26</t>
+          <t>1267885-471-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6921,13 +6921,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1663.73</v>
+        <v>619.29</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1267885-471-CM26</t>
+          <t>1079694-154-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>619.29</v>
+        <v>39101.82</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1079694-154-CM26</t>
+          <t>5418-118-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7043,13 +7043,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>39101.82</v>
+        <v>782.26</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5418-118-CM26</t>
+          <t>5456-37-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>782.26</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5456-37-CM26</t>
+          <t>1079694-184-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7165,13 +7165,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1197.07</v>
+        <v>224.02</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1079694-184-CM26</t>
+          <t>1723-329-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7186,22 +7186,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7226,18 +7226,18 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>224.02</v>
+        <v>12672.11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1723-329-CM26</t>
+          <t>1079694-202-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7247,22 +7247,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7287,13 +7287,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>12672.11</v>
+        <v>37888.82</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1079694-202-CM26</t>
+          <t>1079694-255-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7348,13 +7348,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>37888.82</v>
+        <v>40987.94</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1079694-255-CM26</t>
+          <t>4777-668-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7369,22 +7369,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7409,13 +7409,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>40987.94</v>
+        <v>749.0599999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4777-668-CM26</t>
+          <t>1079694-291-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7430,22 +7430,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7470,13 +7470,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>749.0599999999999</v>
+        <v>38736.49</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1079694-291-CM26</t>
+          <t>5617-26-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7486,27 +7486,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7531,7 +7531,312 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>38736.49</v>
+        <v>10277.8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1079694-313-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>169.33</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2905-639-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>16219.02</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2905-640-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>24328.48</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1079694-331-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>37806.35</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3143-157-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>69.201.100-7</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>33674.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6365,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6426,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6487,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6609,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6853,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6975,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7219,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7280,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7341,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7463,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7585,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7707,7 +8163,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8228,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8293,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -8102,7 +8102,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4062-134-CM25</t>
+          <t>952946-24-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>731.74</v>
+        <v>1045.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>952946-24-CM25</t>
+          <t>4062-134-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1045.34</v>
+        <v>731.74</v>
       </c>
     </row>
     <row r="10">
@@ -1359,7 +1359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>707424-15-CM25</t>
+          <t>4777-1905-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3811.16</v>
+        <v>726.1799999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4777-1905-CM25</t>
+          <t>707424-15-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>726.1799999999999</v>
+        <v>3811.16</v>
       </c>
     </row>
     <row r="17">
@@ -1554,7 +1554,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079694-62-CM25</t>
+          <t>4777-1930-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1156.53</v>
+        <v>13019.4</v>
       </c>
     </row>
     <row r="19">
@@ -1684,7 +1684,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5657-77-CM25</t>
+          <t>1079694-62-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6657.65</v>
+        <v>1156.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4777-1930-CM25</t>
+          <t>5657-77-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13019.4</v>
+        <v>6657.65</v>
       </c>
     </row>
     <row r="22">
@@ -2919,7 +2919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>952946-120-CM25</t>
+          <t>707424-40-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>72222.87</v>
+        <v>568.75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>707424-40-CM25</t>
+          <t>952946-120-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>568.75</v>
+        <v>72222.87</v>
       </c>
     </row>
     <row r="41">
@@ -3244,7 +3244,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3762-3050-CM25</t>
+          <t>5592-3294-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1052.16</v>
+        <v>2725.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5592-3294-CM25</t>
+          <t>3762-3050-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3329,17 +3329,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2725.12</v>
+        <v>1052.16</v>
       </c>
     </row>
     <row r="46">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>952946-46-CM26</t>
+          <t>1079694-83-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1623.96</v>
+        <v>3831.74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4777-243-CM26</t>
+          <t>952946-46-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>10441.82</v>
+        <v>1623.96</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1079694-83-CM26</t>
+          <t>4777-243-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,17 +6319,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3831.74</v>
+        <v>10441.82</v>
       </c>
     </row>
     <row r="92">
@@ -6689,7 +6689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1395865-67-CM26</t>
+          <t>1395865-68-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1395865-68-CM26</t>
+          <t>1395865-67-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8309,6 +8309,266 @@
       </c>
       <c r="M121" s="2" t="n">
         <v>33674.71</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1497-272-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>2317.86</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>707424-86-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>916.5599999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>707424-88-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>2138.65</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1079694-357-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>2039.49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>707424-2-CM25</t>
+          <t>5751-20-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30927.31</v>
+        <v>912.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079694-8-CM25</t>
+          <t>707424-2-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>29803.4</v>
+        <v>30927.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>952946-24-CM25</t>
+          <t>1079694-8-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1045.34</v>
+        <v>29803.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4062-134-CM25</t>
+          <t>952946-24-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>731.74</v>
+        <v>1045.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079694-22-CM25</t>
+          <t>4062-134-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20625.15</v>
+        <v>731.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>952946-41-CM25</t>
+          <t>1079694-22-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1073.96</v>
+        <v>20625.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>952946-46-CM25</t>
+          <t>952946-41-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1072.64</v>
+        <v>1073.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079694-41-CM25</t>
+          <t>952946-46-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>28529.75</v>
+        <v>1072.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>509876-16-CM25</t>
+          <t>1079694-41-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5171.93</v>
+        <v>28529.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4777-1905-CM25</t>
+          <t>509876-16-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>726.1799999999999</v>
+        <v>5171.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>707424-15-CM25</t>
+          <t>4777-1905-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3811.16</v>
+        <v>726.1799999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1192360-20-CM25</t>
+          <t>707424-15-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1116.16</v>
+        <v>3811.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4777-1930-CM25</t>
+          <t>1192360-20-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,27 +1564,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13019.4</v>
+        <v>1116.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4777-1927-CM25</t>
+          <t>4777-1930-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10880.5</v>
+        <v>13019.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079694-62-CM25</t>
+          <t>4777-1927-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1156.53</v>
+        <v>10880.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5657-77-CM25</t>
+          <t>1079694-62-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6657.65</v>
+        <v>1156.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1079694-63-CM25</t>
+          <t>5657-77-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>25387.04</v>
+        <v>6657.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5456-25-CM25</t>
+          <t>1079694-63-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1162.06</v>
+        <v>25387.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5418-59-CM25</t>
+          <t>5456-25-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1515.03</v>
+        <v>1162.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5418-79-CM25</t>
+          <t>5418-59-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3035.96</v>
+        <v>1515.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>707424-25-CM25</t>
+          <t>5418-79-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2805.62</v>
+        <v>3035.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>299-61-CM25</t>
+          <t>707424-25-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>878.96</v>
+        <v>2805.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5472-52-CM25</t>
+          <t>299-61-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2111.91</v>
+        <v>878.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>952946-90-CM25</t>
+          <t>5472-52-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1249.51</v>
+        <v>2111.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079694-96-CM25</t>
+          <t>952946-90-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>24230.83</v>
+        <v>1249.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>952946-99-CM25</t>
+          <t>1079694-96-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3724.71</v>
+        <v>24230.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5742-60-CM25</t>
+          <t>952946-99-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.040-5</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1269.25</v>
+        <v>3724.71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5742-61-CM25</t>
+          <t>5742-60-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>634.62</v>
+        <v>1269.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>299-68-CM25</t>
+          <t>5742-61-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.979.040-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1723.74</v>
+        <v>634.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4062-408-CM25</t>
+          <t>299-68-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>747.3099999999999</v>
+        <v>1723.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>707424-37-CM25</t>
+          <t>4062-408-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>34544.7</v>
+        <v>747.3099999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>299-74-CM25</t>
+          <t>707424-37-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>608.37</v>
+        <v>34544.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>952946-118-CM25</t>
+          <t>299-74-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1596.34</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>707424-40-CM25</t>
+          <t>952946-118-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>568.75</v>
+        <v>1596.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>952946-120-CM25</t>
+          <t>707424-40-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>72222.87</v>
+        <v>568.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1723-411-CM25</t>
+          <t>952946-120-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,13 +3108,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>14568.2</v>
+        <v>72222.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>952946-128-CM25</t>
+          <t>1723-411-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2134.27</v>
+        <v>14568.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1079694-166-CM25</t>
+          <t>952946-128-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>20275.53</v>
+        <v>2134.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5592-3294-CM25</t>
+          <t>1079694-166-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2725.12</v>
+        <v>20275.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3762-3050-CM25</t>
+          <t>5592-3294-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3329,17 +3329,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1052.16</v>
+        <v>2725.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>952946-161-CM25</t>
+          <t>3762-3050-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3389,22 +3389,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1053.82</v>
+        <v>1052.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3762-3087-CM25</t>
+          <t>952946-161-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3454,22 +3454,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25681.75</v>
+        <v>1053.82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079694-241-CM25</t>
+          <t>3762-3087-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3519,22 +3519,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>33850.65</v>
+        <v>25681.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5617-30-CM25</t>
+          <t>1079694-241-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11719.4</v>
+        <v>33850.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4777-2192-CM25</t>
+          <t>5617-30-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>226.78</v>
+        <v>11719.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3789-472-CM25</t>
+          <t>4777-2192-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,27 +3709,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>17083.83</v>
+        <v>226.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3762-3113-CM25</t>
+          <t>3789-472-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2406.34</v>
+        <v>17083.83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1395865-72-CM25</t>
+          <t>3762-3113-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1829.83</v>
+        <v>2406.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1079694-273-CM25</t>
+          <t>1395865-72-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>20672.29</v>
+        <v>1829.83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>952946-189-CM25</t>
+          <t>1079694-273-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2064.77</v>
+        <v>20672.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>952946-192-CM25</t>
+          <t>952946-189-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2072.52</v>
+        <v>2064.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>926853-85-CM25</t>
+          <t>952946-192-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>521.09</v>
+        <v>2072.52</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4777-2354-CM25</t>
+          <t>926853-85-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4169,22 +4169,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>175.79</v>
+        <v>521.09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079694-331-CM25</t>
+          <t>4777-2354-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4234,22 +4234,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>28912.65</v>
+        <v>175.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>952946-204-CM25</t>
+          <t>1079694-331-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>357.03</v>
+        <v>28912.65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079694-351-CM25</t>
+          <t>952946-204-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>24698.16</v>
+        <v>357.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>707424-100-CM25</t>
+          <t>1079694-351-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3128.69</v>
+        <v>24698.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>952946-206-CM25</t>
+          <t>707424-100-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2091.77</v>
+        <v>3128.69</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4777-2444-CM25</t>
+          <t>952946-206-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4559,22 +4559,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2859.91</v>
+        <v>2091.77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>952946-209-CM25</t>
+          <t>4777-2444-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4624,22 +4624,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>47733.45</v>
+        <v>2859.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>707424-103-CM25</t>
+          <t>952946-209-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>26771.84</v>
+        <v>47733.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>952946-220-CM25</t>
+          <t>707424-103-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1589.51</v>
+        <v>26771.84</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1079694-413-CM25</t>
+          <t>952946-220-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>27125.63</v>
+        <v>1589.51</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>299-257-CM25</t>
+          <t>1079694-413-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>24691.78</v>
+        <v>27125.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>952946-230-CM25</t>
+          <t>299-257-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>43990.16</v>
+        <v>24691.78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>952946-236-CM25</t>
+          <t>952946-230-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2152.53</v>
+        <v>43990.16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>766116-2-CM25</t>
+          <t>952946-236-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5074,27 +5074,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>625.98</v>
+        <v>2152.53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1079694-512-CM25</t>
+          <t>766116-2-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5144,22 +5144,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>36214.13</v>
+        <v>625.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>912853-27-SE25</t>
+          <t>1079694-512-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5209,22 +5209,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>53680.23</v>
+        <v>36214.13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1426100-220-CM25</t>
+          <t>912853-27-SE25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5274,22 +5274,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2723.23</v>
+        <v>53680.23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>707424-159-CM25</t>
+          <t>1426100-220-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4561.12</v>
+        <v>2723.23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>952946-1-CM26</t>
+          <t>707424-159-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2218.4</v>
+        <v>4561.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4777-40-CM26</t>
+          <t>952946-1-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5469,22 +5469,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11107.26</v>
+        <v>2218.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4777-41-CM26</t>
+          <t>4777-40-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>26974.77</v>
+        <v>11107.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1079694-17-CM26</t>
+          <t>4777-41-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>45824.67</v>
+        <v>26974.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1079694-46-CM26</t>
+          <t>1079694-17-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>30448.31</v>
+        <v>45824.67</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5751-39-CM26</t>
+          <t>1079694-46-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1065.39</v>
+        <v>30448.31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4777-170-CM26</t>
+          <t>5751-39-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5794,22 +5794,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8121.92</v>
+        <v>1065.39</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>952946-21-CM26</t>
+          <t>4777-170-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2332.14</v>
+        <v>8121.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>952946-22-CM26</t>
+          <t>952946-21-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1655.04</v>
+        <v>2332.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1079694-76-CM26</t>
+          <t>952946-22-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>26376.07</v>
+        <v>1655.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1192360-14-CM26</t>
+          <t>1079694-76-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1262.48</v>
+        <v>26376.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>926853-3-CM26</t>
+          <t>1192360-14-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1368.43</v>
+        <v>1262.48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1079694-83-CM26</t>
+          <t>926853-3-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3831.74</v>
+        <v>1368.43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>952946-46-CM26</t>
+          <t>1079694-83-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1623.96</v>
+        <v>3831.74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4777-243-CM26</t>
+          <t>952946-46-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,17 +6319,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10441.82</v>
+        <v>1623.96</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1079694-88-CM26</t>
+          <t>4777-243-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6379,22 +6379,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1322.35</v>
+        <v>10441.82</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>509876-20-CM26</t>
+          <t>1079694-88-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5169.55</v>
+        <v>1322.35</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5418-63-CM26</t>
+          <t>509876-20-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1252.45</v>
+        <v>5169.55</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>707424-15-CM26</t>
+          <t>5418-63-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6574,22 +6574,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>100669.25</v>
+        <v>1252.45</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>707424-20-CM26</t>
+          <t>707424-15-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3058.03</v>
+        <v>100669.25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1395865-68-CM26</t>
+          <t>707424-20-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6704,22 +6704,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2668.67</v>
+        <v>3058.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1395865-67-CM26</t>
+          <t>1395865-68-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1079694-104-CM26</t>
+          <t>1395865-67-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6834,22 +6834,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>38144.81</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>952946-63-CM26</t>
+          <t>1079694-104-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2257.11</v>
+        <v>38144.81</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>926853-10-CM26</t>
+          <t>952946-63-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>563.77</v>
+        <v>2257.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>952946-76-CM26</t>
+          <t>926853-10-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1246.83</v>
+        <v>563.77</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5418-93-CM26</t>
+          <t>952946-76-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1574.62</v>
+        <v>1246.83</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5418-94-CM26</t>
+          <t>5418-93-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1443.4</v>
+        <v>1574.62</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>952946-87-CM26</t>
+          <t>5418-94-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1663.73</v>
+        <v>1443.4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1267885-471-CM26</t>
+          <t>952946-87-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>619.29</v>
+        <v>1663.73</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1079694-154-CM26</t>
+          <t>1267885-471-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>39101.82</v>
+        <v>619.29</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5418-118-CM26</t>
+          <t>1079694-154-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>782.26</v>
+        <v>39101.82</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5456-37-CM26</t>
+          <t>5418-118-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1197.07</v>
+        <v>782.26</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079694-184-CM26</t>
+          <t>5456-37-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>224.02</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1723-329-CM26</t>
+          <t>1079694-184-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7614,22 +7614,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,18 +7658,18 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12672.11</v>
+        <v>224.02</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1079694-202-CM26</t>
+          <t>1723-329-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>37888.82</v>
+        <v>12672.11</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1079694-255-CM26</t>
+          <t>1079694-202-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>40987.94</v>
+        <v>37888.82</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4777-668-CM26</t>
+          <t>1079694-255-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7809,22 +7809,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>749.0599999999999</v>
+        <v>40987.94</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1079694-291-CM26</t>
+          <t>4777-668-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7874,22 +7874,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>38736.49</v>
+        <v>749.0599999999999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5617-26-CM26</t>
+          <t>1079694-291-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7934,27 +7934,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>10277.8</v>
+        <v>38736.49</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1079694-313-CM26</t>
+          <t>5617-26-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8004,22 +8004,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,13 +8048,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>169.33</v>
+        <v>10277.8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2905-639-CM26</t>
+          <t>1079694-313-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8094,17 +8094,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>16219.02</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2905-640-CM26</t>
+          <t>2905-639-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8178,13 +8178,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>24328.48</v>
+        <v>16219.02</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1079694-331-CM26</t>
+          <t>2905-640-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8199,22 +8199,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>37806.35</v>
+        <v>24328.48</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3143-157-CM26</t>
+          <t>1079694-331-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8264,22 +8264,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>33674.71</v>
+        <v>37806.35</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1497-272-CM26</t>
+          <t>3143-157-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2317.86</v>
+        <v>33674.71</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>707424-86-CM26</t>
+          <t>1497-272-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>916.5599999999999</v>
+        <v>2317.86</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>707424-88-CM26</t>
+          <t>707424-86-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8503,71 +8503,136 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2138.65</v>
+        <v>916.5599999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>707424-88-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>2138.65</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>1079694-357-CM26</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>60.505.523-0</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M125" s="2" t="n">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
         <v>2039.49</v>
       </c>
     </row>
